--- a/assets/downloads/Beispiel_KTR_Konverter.xlsx
+++ b/assets/downloads/Beispiel_KTR_Konverter.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Config\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\handbook\assets\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307018D8-4DB1-46AB-AB46-FD4E350DE9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF5C7DF-0489-424A-8DEE-34DB960E78FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{A5C741B9-029C-4B51-8443-C30E7A1866D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5C741B9-029C-4B51-8443-C30E7A1866D3}"/>
   </bookViews>
   <sheets>
-    <sheet name="SpiGes-400-KostentraegerStandor" sheetId="1" r:id="rId1"/>
+    <sheet name="KTR_Konverter" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/assets/downloads/Beispiel_KTR_Konverter.xlsx
+++ b/assets/downloads/Beispiel_KTR_Konverter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\handbook\assets\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF5C7DF-0489-424A-8DEE-34DB960E78FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4473F69-4E97-42DF-A449-69CD946F2F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5C741B9-029C-4B51-8443-C30E7A1866D3}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{A5C741B9-029C-4B51-8443-C30E7A1866D3}"/>
   </bookViews>
   <sheets>
     <sheet name="KTR_Konverter" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
   <si>
     <t>ent_id</t>
   </si>
@@ -335,6 +335,15 @@
   </si>
   <si>
     <t>Formation post-grade CHR</t>
+  </si>
+  <si>
+    <t>ktr_47</t>
+  </si>
+  <si>
+    <t>ktr_47_ank</t>
+  </si>
+  <si>
+    <t>ktr_vvg_al</t>
   </si>
 </sst>
 </file>
@@ -1195,13 +1204,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FCB1FF-6035-49F1-8928-3BC027CCE491}">
-  <dimension ref="A1:CT10"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1496,8 +1505,17 @@
       <c r="CT1" t="s">
         <v>97</v>
       </c>
+      <c r="CU1" t="s">
+        <v>105</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>106</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>107</v>
+      </c>
     </row>
-    <row r="2" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>100392723</v>
       </c>
@@ -1789,8 +1807,17 @@
       <c r="CT2">
         <v>0</v>
       </c>
+      <c r="CU2">
+        <v>0</v>
+      </c>
+      <c r="CV2">
+        <v>0</v>
+      </c>
+      <c r="CW2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>100392723</v>
       </c>
@@ -2082,8 +2109,17 @@
       <c r="CT3">
         <v>0</v>
       </c>
+      <c r="CU3">
+        <v>0</v>
+      </c>
+      <c r="CV3">
+        <v>0</v>
+      </c>
+      <c r="CW3">
+        <v>250</v>
+      </c>
     </row>
-    <row r="4" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>100392723</v>
       </c>
@@ -2375,8 +2411,17 @@
       <c r="CT4">
         <v>5</v>
       </c>
+      <c r="CU4">
+        <v>0</v>
+      </c>
+      <c r="CV4">
+        <v>0</v>
+      </c>
+      <c r="CW4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>100392723</v>
       </c>
@@ -2668,8 +2713,17 @@
       <c r="CT5">
         <v>0</v>
       </c>
+      <c r="CU5">
+        <v>0</v>
+      </c>
+      <c r="CV5">
+        <v>0</v>
+      </c>
+      <c r="CW5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>100392723</v>
       </c>
@@ -2964,8 +3018,17 @@
       <c r="CT6">
         <v>5</v>
       </c>
+      <c r="CU6">
+        <v>265555</v>
+      </c>
+      <c r="CV6">
+        <v>0</v>
+      </c>
+      <c r="CW6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>100392723</v>
       </c>
@@ -3260,8 +3323,17 @@
       <c r="CT7">
         <v>5</v>
       </c>
+      <c r="CU7">
+        <v>0</v>
+      </c>
+      <c r="CV7">
+        <v>0</v>
+      </c>
+      <c r="CW7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>100392723</v>
       </c>
@@ -3556,8 +3628,17 @@
       <c r="CT8">
         <v>5</v>
       </c>
+      <c r="CU8">
+        <v>0</v>
+      </c>
+      <c r="CV8">
+        <v>0</v>
+      </c>
+      <c r="CW8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>100392723</v>
       </c>
@@ -3852,8 +3933,17 @@
       <c r="CT9">
         <v>5</v>
       </c>
+      <c r="CU9">
+        <v>0</v>
+      </c>
+      <c r="CV9">
+        <v>0</v>
+      </c>
+      <c r="CW9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>100392723</v>
       </c>
@@ -4147,6 +4237,15 @@
       </c>
       <c r="CT10">
         <v>5</v>
+      </c>
+      <c r="CU10">
+        <v>0</v>
+      </c>
+      <c r="CV10">
+        <v>0</v>
+      </c>
+      <c r="CW10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/assets/downloads/Beispiel_KTR_Konverter.xlsx
+++ b/assets/downloads/Beispiel_KTR_Konverter.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\handbook\assets\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4473F69-4E97-42DF-A449-69CD946F2F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE62F52E-242A-4FFD-AE5D-6CF7291D1876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{A5C741B9-029C-4B51-8443-C30E7A1866D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5C741B9-029C-4B51-8443-C30E7A1866D3}"/>
   </bookViews>
   <sheets>
     <sheet name="KTR_Konverter" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" concurrentManualCount="8"/>
 </workbook>
 </file>
 
@@ -343,7 +343,7 @@
     <t>ktr_47_ank</t>
   </si>
   <si>
-    <t>ktr_vvg_al</t>
+    <t>ktr_al_vvg</t>
   </si>
 </sst>
 </file>

--- a/assets/downloads/Beispiel_KTR_Konverter.xlsx
+++ b/assets/downloads/Beispiel_KTR_Konverter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\handbook\assets\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE62F52E-242A-4FFD-AE5D-6CF7291D1876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426C7CE7-C39C-4E5A-A4F9-F081A7C0CE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5C741B9-029C-4B51-8443-C30E7A1866D3}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{A5C741B9-029C-4B51-8443-C30E7A1866D3}"/>
   </bookViews>
   <sheets>
     <sheet name="KTR_Konverter" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>ent_id</t>
   </si>
@@ -316,27 +316,12 @@
     <t>ktr_methodik</t>
   </si>
   <si>
-    <t>Autres tarifs amb. sp‚cifiques … l'‚tablissement 1, LAMal purement AOS (co–t par cas)</t>
-  </si>
-  <si>
     <t>PIG</t>
   </si>
   <si>
     <t>Tarif TARMED, CTM</t>
   </si>
   <si>
-    <t>Formation pr‚grade CHR</t>
-  </si>
-  <si>
-    <t>Recherche CHR</t>
-  </si>
-  <si>
-    <t>Restauration CDF</t>
-  </si>
-  <si>
-    <t>Formation post-grade CHR</t>
-  </si>
-  <si>
     <t>ktr_47</t>
   </si>
   <si>
@@ -344,6 +329,27 @@
   </si>
   <si>
     <t>ktr_al_vvg</t>
+  </si>
+  <si>
+    <t>Tarif TARMED, KVG reine OKP</t>
+  </si>
+  <si>
+    <t>Tarif TARMED, personne payant elle-même, incl. personnes avec assurance complémentaire</t>
+  </si>
+  <si>
+    <t>Erteilte und erhaltene universitäre Ausbildung</t>
+  </si>
+  <si>
+    <t>Formation universitaire de base (enseignement dispensé et formation reçue)</t>
+  </si>
+  <si>
+    <t>Restauration</t>
+  </si>
+  <si>
+    <t>Restauration SITE</t>
+  </si>
+  <si>
+    <t>Geburtshilfe</t>
   </si>
 </sst>
 </file>
@@ -1506,24 +1512,24 @@
         <v>97</v>
       </c>
       <c r="CU1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="CV1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="CW1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>100392723</v>
+        <v>100000000</v>
       </c>
       <c r="C2">
-        <v>372</v>
+        <v>301</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1819,13 +1825,13 @@
     </row>
     <row r="3" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>100392723</v>
+        <v>100000000</v>
       </c>
       <c r="C3">
-        <v>373</v>
+        <v>303</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -2121,13 +2127,13 @@
     </row>
     <row r="4" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>100392723</v>
+        <v>100000000</v>
       </c>
       <c r="C4">
         <v>599</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -2423,13 +2429,13 @@
     </row>
     <row r="5" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>100392723</v>
+        <v>100000000</v>
       </c>
       <c r="C5">
         <v>302</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E5">
         <v>10000</v>
@@ -2725,16 +2731,16 @@
     </row>
     <row r="6" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>100392723</v>
+        <v>100000000</v>
       </c>
       <c r="B6">
-        <v>40787360</v>
+        <v>40000000</v>
       </c>
       <c r="C6">
         <v>602</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -3030,16 +3036,16 @@
     </row>
     <row r="7" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>100392723</v>
+        <v>100000000</v>
       </c>
       <c r="B7">
-        <v>40787360</v>
+        <v>40000000</v>
       </c>
       <c r="C7">
         <v>601</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3335,16 +3341,16 @@
     </row>
     <row r="8" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>100392723</v>
+        <v>100000000</v>
       </c>
       <c r="B8">
-        <v>40787360</v>
+        <v>40000000</v>
       </c>
       <c r="C8">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -3640,16 +3646,16 @@
     </row>
     <row r="9" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>100392723</v>
+        <v>100000000</v>
       </c>
       <c r="B9">
-        <v>40787360</v>
+        <v>40000000</v>
       </c>
       <c r="C9">
-        <v>603</v>
+        <v>702</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -3945,16 +3951,16 @@
     </row>
     <row r="10" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>100392723</v>
+        <v>100000000</v>
       </c>
       <c r="B10">
-        <v>42018772</v>
+        <v>40000001</v>
       </c>
       <c r="C10">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E10">
         <v>0</v>
